--- a/Simulator/results.xlsx
+++ b/Simulator/results.xlsx
@@ -1,29 +1,98 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10625"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/A19BA2A0922A26C9/Documenti/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="192" documentId="8_{92B70B09-2A99-4EC5-8AA5-3B7F9CDE5885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F10EB52-6726-7D45-A241-763ED9EA24C2}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="OptimFALSE" sheetId="1" r:id="rId1"/>
+    <sheet name="OptimTRUE" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+  <si>
+    <t>THROUGHPUT</t>
+  </si>
+  <si>
+    <t>SCENARIO</t>
+  </si>
+  <si>
+    <t>seed343310</t>
+  </si>
+  <si>
+    <t>seed300871</t>
+  </si>
+  <si>
+    <t>seed030201</t>
+  </si>
+  <si>
+    <t>seed301060</t>
+  </si>
+  <si>
+    <t>seed050102</t>
+  </si>
+  <si>
+    <t>seed293874</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -49,11 +118,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +406,579 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.28125" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="10.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>593</v>
+      </c>
+      <c r="C5">
+        <v>596</v>
+      </c>
+      <c r="D5">
+        <v>596</v>
+      </c>
+      <c r="E5">
+        <v>585</v>
+      </c>
+      <c r="F5">
+        <v>598</v>
+      </c>
+      <c r="G5">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>602</v>
+      </c>
+      <c r="C6">
+        <v>588</v>
+      </c>
+      <c r="D6">
+        <v>582</v>
+      </c>
+      <c r="E6">
+        <v>598</v>
+      </c>
+      <c r="F6">
+        <v>595</v>
+      </c>
+      <c r="G6">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>596</v>
+      </c>
+      <c r="C7">
+        <v>608</v>
+      </c>
+      <c r="D7">
+        <v>602</v>
+      </c>
+      <c r="E7">
+        <v>576</v>
+      </c>
+      <c r="F7">
+        <v>609</v>
+      </c>
+      <c r="G7">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>601</v>
+      </c>
+      <c r="C8">
+        <v>600</v>
+      </c>
+      <c r="D8">
+        <v>599</v>
+      </c>
+      <c r="E8">
+        <v>590</v>
+      </c>
+      <c r="F8">
+        <v>616</v>
+      </c>
+      <c r="G8">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>535</v>
+      </c>
+      <c r="C10">
+        <v>538</v>
+      </c>
+      <c r="D10">
+        <v>541</v>
+      </c>
+      <c r="E10">
+        <v>539</v>
+      </c>
+      <c r="F10">
+        <v>533</v>
+      </c>
+      <c r="G10">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>12</v>
+      </c>
+      <c r="B11">
+        <v>542</v>
+      </c>
+      <c r="C11">
+        <v>526</v>
+      </c>
+      <c r="D11">
+        <v>535</v>
+      </c>
+      <c r="E11">
+        <v>527</v>
+      </c>
+      <c r="F11">
+        <v>530</v>
+      </c>
+      <c r="G11">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>13</v>
+      </c>
+      <c r="B12">
+        <v>525</v>
+      </c>
+      <c r="C12">
+        <v>538</v>
+      </c>
+      <c r="D12">
+        <v>544</v>
+      </c>
+      <c r="E12">
+        <v>534</v>
+      </c>
+      <c r="F12">
+        <v>542</v>
+      </c>
+      <c r="G12">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <v>530</v>
+      </c>
+      <c r="C13">
+        <v>526</v>
+      </c>
+      <c r="D13">
+        <v>544</v>
+      </c>
+      <c r="E13">
+        <v>537</v>
+      </c>
+      <c r="F13">
+        <v>515</v>
+      </c>
+      <c r="G13">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>21</v>
+      </c>
+      <c r="B15">
+        <v>477</v>
+      </c>
+      <c r="C15">
+        <v>476</v>
+      </c>
+      <c r="D15">
+        <v>472</v>
+      </c>
+      <c r="E15">
+        <v>468</v>
+      </c>
+      <c r="F15">
+        <v>461</v>
+      </c>
+      <c r="G15">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>22</v>
+      </c>
+      <c r="B16">
+        <v>478</v>
+      </c>
+      <c r="C16">
+        <v>477</v>
+      </c>
+      <c r="D16">
+        <v>474</v>
+      </c>
+      <c r="E16">
+        <v>473</v>
+      </c>
+      <c r="F16">
+        <v>468</v>
+      </c>
+      <c r="G16">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>23</v>
+      </c>
+      <c r="B17">
+        <v>465</v>
+      </c>
+      <c r="C17">
+        <v>465</v>
+      </c>
+      <c r="D17">
+        <v>477</v>
+      </c>
+      <c r="E17">
+        <v>466</v>
+      </c>
+      <c r="F17">
+        <v>462</v>
+      </c>
+      <c r="G17">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>24</v>
+      </c>
+      <c r="B18">
+        <v>478</v>
+      </c>
+      <c r="C18">
+        <v>466</v>
+      </c>
+      <c r="D18">
+        <v>483</v>
+      </c>
+      <c r="E18">
+        <v>470</v>
+      </c>
+      <c r="F18">
+        <v>472</v>
+      </c>
+      <c r="G18">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>31</v>
+      </c>
+      <c r="B20">
+        <v>438</v>
+      </c>
+      <c r="C20">
+        <v>427</v>
+      </c>
+      <c r="D20">
+        <v>428</v>
+      </c>
+      <c r="E20">
+        <v>432</v>
+      </c>
+      <c r="F20">
+        <v>435</v>
+      </c>
+      <c r="G20">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>32</v>
+      </c>
+      <c r="B21">
+        <v>436</v>
+      </c>
+      <c r="C21">
+        <v>431</v>
+      </c>
+      <c r="D21">
+        <v>427</v>
+      </c>
+      <c r="E21">
+        <v>420</v>
+      </c>
+      <c r="F21">
+        <v>434</v>
+      </c>
+      <c r="G21">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>33</v>
+      </c>
+      <c r="B22">
+        <v>439</v>
+      </c>
+      <c r="C22">
+        <v>431</v>
+      </c>
+      <c r="D22">
+        <v>429</v>
+      </c>
+      <c r="E22">
+        <v>442</v>
+      </c>
+      <c r="F22">
+        <v>443</v>
+      </c>
+      <c r="G22">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>34</v>
+      </c>
+      <c r="B23">
+        <v>433</v>
+      </c>
+      <c r="C23">
+        <v>436</v>
+      </c>
+      <c r="D23">
+        <v>451</v>
+      </c>
+      <c r="E23">
+        <v>432</v>
+      </c>
+      <c r="F23">
+        <v>434</v>
+      </c>
+      <c r="G23">
+        <v>439</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27629085-A2E6-4F54-9253-F3C5B6DC3FB0}">
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.28125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.76171875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.76171875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>11</v>
+      </c>
+      <c r="F10">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>13</v>
+      </c>
+      <c r="F12">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>14</v>
+      </c>
+      <c r="F13">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>21</v>
+      </c>
+      <c r="F15">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>22</v>
+      </c>
+      <c r="F16">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>23</v>
+      </c>
+      <c r="F17">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>24</v>
+      </c>
+      <c r="F18">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>31</v>
+      </c>
+      <c r="F20">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>32</v>
+      </c>
+      <c r="F21">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>33</v>
+      </c>
+      <c r="F22">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>34</v>
+      </c>
+      <c r="F23">
+        <v>491</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Simulator/results.xlsx
+++ b/Simulator/results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10625"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/A19BA2A0922A26C9/Documenti/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chiod\Documents\OMERO_TaskDesign\Simulator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="192" documentId="8_{92B70B09-2A99-4EC5-8AA5-3B7F9CDE5885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F10EB52-6726-7D45-A241-763ED9EA24C2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A787C5-4C10-49ED-B91D-51DD4382BBE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="16910" windowHeight="8840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OptimFALSE" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="8">
   <si>
     <t>THROUGHPUT</t>
   </si>
@@ -129,7 +129,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -408,20 +408,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28125" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -444,7 +444,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
@@ -467,7 +467,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2</v>
       </c>
@@ -490,7 +490,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>3</v>
       </c>
@@ -513,7 +513,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>4</v>
       </c>
@@ -536,7 +536,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>11</v>
       </c>
@@ -559,7 +559,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>12</v>
       </c>
@@ -582,7 +582,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>13</v>
       </c>
@@ -605,7 +605,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>14</v>
       </c>
@@ -628,7 +628,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>22</v>
       </c>
@@ -674,7 +674,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>23</v>
       </c>
@@ -697,7 +697,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>24</v>
       </c>
@@ -720,7 +720,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>31</v>
       </c>
@@ -743,7 +743,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>32</v>
       </c>
@@ -766,7 +766,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>33</v>
       </c>
@@ -789,7 +789,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>34</v>
       </c>
@@ -823,154 +823,168 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27629085-A2E6-4F54-9253-F3C5B6DC3FB0}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.76171875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.76171875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
       <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>594</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>588</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>3</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>643</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>4</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>552</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>11</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>519</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>12</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>575</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>13</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>606</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>14</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>574</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>21</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>478</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>22</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>501</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>23</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>499</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>24</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>515</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>31</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>418</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>32</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>485</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>33</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>486</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>34</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>491</v>
       </c>
     </row>
